--- a/reports/brand24/toyota_report_2026-09-15_to_2026-09-16.xlsx
+++ b/reports/brand24/toyota_report_2026-09-15_to_2026-09-16.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="643">
   <si>
     <t>ID</t>
   </si>
@@ -54,24 +54,183 @@
     <t>2026-09-15</t>
   </si>
   <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>jessburtonx</t>
+  </si>
+  <si>
+    <t>Day 2 of using engagements for the Daihatsu Project #fyp #fund # daihatsu</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@jessburtonx/video/7685863005770370326</t>
+  </si>
+  <si>
+    <t>tiktok.com</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099938677858156979</t>
+  </si>
+  <si>
+    <t>x.com</t>
+  </si>
+  <si>
+    <t>X (Twitter)</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>O M N I V E R S E</t>
+  </si>
+  <si>
+    <t>One of them had ... [...] It tilted its head curiously, as though it had just found the most precious toy in an endless cosmic wasteland. Here—this was the only thing in the entire expanse of dust and empty meteorites that did not resemble anything else</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/u_Drizzle9696/comments/1wh94k5/o_m_n_i_v_e_r_s_e</t>
+  </si>
+  <si>
+    <t>reddit.com</t>
+  </si>
+  <si>
+    <t>Other Socials</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099928232288223462</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099926778525753731</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099924400019796349</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099921748594766311</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099915727759429788</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>1efficentautosales</t>
+  </si>
+  <si>
+    <t>2016 Daihatsu Mira $110,000JMD CLEARANCE MEGA HOT SALE🚨‼️ ✅Excellent Condition ✅Solid Engine and Transmission ✅Accident Free ✅AC Cold🥶 ✅Reverse Camera ✅Good Mileage ✅Key Start ✅Multifunctional Steering Wheel ✅Clean Interior #1efficientautosales #jama</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@1efficentautosales/video/7685813555957927175</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>t.mechanic07</t>
+  </si>
+  <si>
+    <t>service on a Toyota c-hr #viral #fyp # toyota #chr #mechanics</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@t.mechanic07/video/7685811896829906178</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>daisythecopen</t>
+  </si>
+  <si>
+    <t>#tractor # daihatsu #keicar #tinycar #daihatsucopen</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@daisythecopen/video/7685811108267019542</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099908251823599696</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099905413059899667</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099905337495306508</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099901163886031086</t>
+  </si>
+  <si>
     <t>09:33</t>
   </si>
   <si>
     <t>Tweet-ID: 2099899490736222505</t>
   </si>
   <si>
-    <t>x.com</t>
-  </si>
-  <si>
-    <t>X (Twitter)</t>
-  </si>
-  <si>
     <t>09:27</t>
   </si>
   <si>
     <t>Tweet-ID: 2099897942027227622</t>
   </si>
   <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>Xe NÃ¢ng Dáº§u Toyota 7FD25 2.5 Táº¥n</t>
+  </si>
+  <si>
+    <t>[...] kiá»ƒm tra khi mua xe nÃ¢ng Toyota 7FD25 Ä‘Ã£ qua sá» dá»¥ngNháº¥t Lá»™c PhÃ¡t cung cáº¥p xe nÃ¢ng Toyota 7FD25 chÃnh hÃ£ngXe nÃ¢ng dáº§u Toyota 7fd25 2.5 táº¥n lÃ dÃ²ng xe nÃ¢ng Ä‘Æ°á»£c nhiá»u doanh nghiá»‡p lá»±a chá»n cho cÃ ng viá»‡c bá»</t>
+  </si>
+  <si>
+    <t>https://xenangnhatlocphat.vn/san-pham/xe-nang-dau-toyota-7fd25-2-5-tan</t>
+  </si>
+  <si>
+    <t>xenangnhatlocphat.vn</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099890332309819899</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099886657541730804</t>
+  </si>
+  <si>
     <t>08:36</t>
   </si>
   <si>
@@ -84,10 +243,22 @@
     <t>https://www.tiktok.com/@ranaarham0672/video/7685786299982155026</t>
   </si>
   <si>
-    <t>tiktok.com</t>
-  </si>
-  <si>
-    <t>TikTok</t>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099883565555372366</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>reviewbaogiaxetoyota</t>
+  </si>
+  <si>
+    <t>Toyota vừa chốt hạ Land Cruiser LC 300 HEV# toyota #landcruiser</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@reviewbaogiaxetoyota/video/7685783884327390472</t>
   </si>
   <si>
     <t>08:19</t>
@@ -120,6 +291,18 @@
     <t>https://www.tiktok.com/@daily.laughs42/video/7685780625558637846</t>
   </si>
   <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>detail_district12</t>
+  </si>
+  <si>
+    <t>yes the boys toyota yaris in for an outside detail #getbookedin #14 #detail_district12 #detailer #fyp</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@detail_district12/video/7685779798173551894</t>
+  </si>
+  <si>
     <t>07:58</t>
   </si>
   <si>
@@ -138,6 +321,27 @@
     <t>News</t>
   </si>
   <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>Tweet-ID: 2099873658458231022</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>5 mẫu SUV máy xăng, dầu bán chạy nhất tháng Ngâu</t>
+  </si>
+  <si>
+    <t>Mazda CX-5 vẫn dẫn đầu nhóm này, trong khi Toyota Yaris Cross giảm mạnh so với tháng trước</t>
+  </si>
+  <si>
+    <t>https://thanhnien.vn/5-mau-suv-may-xang-dau-ban-chay-nhat-thang-ngau-185260915125230771.htm</t>
+  </si>
+  <si>
+    <t>thanhnien.vn</t>
+  </si>
+  <si>
     <t>07:38</t>
   </si>
   <si>
@@ -171,6 +375,42 @@
     <t>https://www.tiktok.com/@ra.1829.onworld/video/7685769312631557408</t>
   </si>
   <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>khidriftkings</t>
+  </si>
+  <si>
+    <t>Toyota Always king 👑💀🙌🏻 #carsofpakistan #fyp # toyota #always #king</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@khidriftkings_/video/7685768956065385750</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>carzstore.pk2</t>
+  </si>
+  <si>
+    <t>Toyota Yaris is here for some interior upgrades ✨✅ #caraccessories #carmodification #modifiedcars #foryou #carzstorepk</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@carzstore.pk2/video/7685767951290469653</t>
+  </si>
+  <si>
+    <t>07:17</t>
+  </si>
+  <si>
+    <t>courtesytoyotabrandon</t>
+  </si>
+  <si>
+    <t>2026 Toyota Tacoma TRD Sport ASMR . TSRP as shown $52,421 . Assembled in BAJA CALF, MEXICO . Color: CELESTIAL SILVER/EA20 . #asmr # toyota #tacoma #toyotatacoma #trdsport</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@courtesytoyotabrandon/video/7685526432835046670</t>
+  </si>
+  <si>
     <t>07:05</t>
   </si>
   <si>
@@ -183,6 +423,18 @@
     <t>http://www.youtube.com/watch?v=B5rR5USlGI8&amp;t=1080s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>jeyshkagarcia</t>
+  </si>
+  <si>
+    <t>🚗 2025 Toyota Corolla LE — CERTIFIED ✔️ 68,000 miles ✔️ Toyota Certified Used Vehicle ✔️ Excellent fuel economy ✔️ Reliable &amp; affordable ✔️ Great daily driver Looking for a dependable Corolla without paying new-car pricing? This one is worth checking</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@jeyshkagarcia/video/7685759302212029726</t>
+  </si>
+  <si>
     <t>06:47</t>
   </si>
   <si>
@@ -219,6 +471,18 @@
     <t>http://www.youtube.com/watch?v=ZfKrotz64x0&amp;t=6s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>lha_0603</t>
+  </si>
+  <si>
+    <t>Land Cruiser LC300 2025. Các bác quan tâm liên hệ em ạ. #Hoanganhlexusluot # toyota #lc300 #xuhuong #hanoicar</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@lha_0603/video/7685756269667355925</t>
+  </si>
+  <si>
     <t>06:33</t>
   </si>
   <si>
@@ -231,6 +495,18 @@
     <t>https://www.tiktok.com/@luxurycar4u/video/7685754462870244621</t>
   </si>
   <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>atthawetnuamthong</t>
+  </si>
+  <si>
+    <t># toyota #yariscross #yariscrosshybrid #toyotahev</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@atthawetnuamthong/video/7685751394657111304</t>
+  </si>
+  <si>
     <t>06:15</t>
   </si>
   <si>
@@ -243,6 +519,30 @@
     <t>https://www.tiktok.com/@tabishbintahir441/video/7685713086317186312</t>
   </si>
   <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>thanhnam.chuyenxesang</t>
+  </si>
+  <si>
+    <t>Sức hấp dẫn khó tả Toyota Land Cruiser LC 300 HEV Xe sẳn sàng phục vụ các Chủ tịch #LC300HEV#Landcruiser#ThànhNamToyota #giaongay</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@thanhnam.chuyenxesang/video/7685749756794260757</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>mgkoeww</t>
+  </si>
+  <si>
+    <t>ကို့ရဲ့လက်ရာကိုယ်ပြန်ကြွေ💪🤩🔥#ဝါသနာအရ # toyota #supra #car</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@mgkoeww/video/7685747277184388372</t>
+  </si>
+  <si>
     <t>06:00</t>
   </si>
   <si>
@@ -306,6 +606,15 @@
     <t>05:52</t>
   </si>
   <si>
+    <t>zorro.auto</t>
+  </si>
+  <si>
+    <t>Toyota RAV4 — a popular choice around the world. 🌍 Different countries, different roads, but people still love the RAV4. Where are you watching from? 👋 #ToyotaRAV4 #RAV4 # Toyota #SUV #GlobalCars</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@zorro.auto/video/7685744109620890901</t>
+  </si>
+  <si>
     <t>Tweet-ID: 2099843730945552668</t>
   </si>
   <si>
@@ -351,18 +660,66 @@
     <t>https://www.tiktok.com/@ngn.xe.sang/video/7685738222042844437</t>
   </si>
   <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>user842797299774</t>
+  </si>
+  <si>
+    <t>Toyota yaris #car #cars # toyota #meme #funny #trending #bemngdrive</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@user842797299774/video/7685737262981647638</t>
+  </si>
+  <si>
     <t>05:25</t>
   </si>
   <si>
     <t>Tweet-ID: 2099836975285215536</t>
   </si>
   <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>hgina_55</t>
+  </si>
+  <si>
+    <t>bored#hgina_55 #powerrangers #kyoryuger #dinochargeranger # toy</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@hgina_55/video/7685736866930380040</t>
+  </si>
+  <si>
     <t>05:22</t>
   </si>
   <si>
     <t>Tweet-ID: 2099836352187764747</t>
   </si>
   <si>
+    <t>Disneyland Paris : những trò chơi nào có thể tiếp cận bằng vé bỏ qua hàng Disney Premier Access?</t>
+  </si>
+  <si>
+    <t>cảm giác và mẹo để làm chủ chiếc xe đua Toy StoryLên tàu siêu xe điều khiển từ xa của Andy</t>
+  </si>
+  <si>
+    <t>https://www.sortiraparis.com/vi/nghe-thuat-van-hoa/di-bo-va-cong-vien/articles/352193-disneyland-paris-nhung-tro-choi-nao-duoc-truy-cap-voi-quyen-uu-tien-disney-premier-access</t>
+  </si>
+  <si>
+    <t>sortiraparis.com</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>duhaotoyota</t>
+  </si>
+  <si>
+    <t>TOYOTA INNOVA CROSS 2.0 HYBRID 2026 CÓ GÌ ? #innovacross #toyotainnova # toyota #tuvanxe #oto</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@duhaotoyota/video/7685736043349282056</t>
+  </si>
+  <si>
     <t>05:19</t>
   </si>
   <si>
@@ -375,6 +732,18 @@
     <t>https://www.tiktok.com/@bss.tqdk/video/7685735403155983630</t>
   </si>
   <si>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>meryy.berry</t>
+  </si>
+  <si>
+    <t>Avec la Toyota C-HR, les petits plans spontanés deviennent encore plus faciles ✨@ Toyota Canada #Ad # Toyota #PartenaireToyota #VoitureÉlectrique</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@meryy.berry/video/7685735006509108500</t>
+  </si>
+  <si>
     <t>05:15</t>
   </si>
   <si>
@@ -399,12 +768,36 @@
     <t>https://www.tiktok.com/@fix.carkeys/video/7685732672617860374</t>
   </si>
   <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>jdm_szene_ost</t>
+  </si>
+  <si>
+    <t>The Toyota Supra never gets old. #toyotasupra #toyotasupramk4 #toyotasupramk5 #supra #2jz</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@jdm_szene_ost_/video/7685730306988576033</t>
+  </si>
+  <si>
     <t>04:49</t>
   </si>
   <si>
     <t>Tweet-ID: 2099827835158630466</t>
   </si>
   <si>
+    <t>04:43</t>
+  </si>
+  <si>
+    <t>eulollagomes</t>
+  </si>
+  <si>
+    <t>#foryoo#fy#sw4# toyota</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@eulollagomes/video/7685726197271072021</t>
+  </si>
+  <si>
     <t>04:41</t>
   </si>
   <si>
@@ -555,6 +948,24 @@
     <t>Tweet-ID: 2099816095142105189</t>
   </si>
   <si>
+    <t>facebook.com</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>toyotauae</t>
+  </si>
+  <si>
+    <t>That first walk towards your all-new Toyota RAV4 hits a little differently. Take a second. You’ve earned this feeling. تلك اللحظة الأولى التي تسير فيها باتجاه سيارتك تويوتا راف 4 الجديدة كلياً، لها وقع مختلف. تمهل قليلاً وعش اللحظة. أنت تستحق الاستمت</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@toyotauae/video/7685715479691889941</t>
+  </si>
+  <si>
     <t>04:00</t>
   </si>
   <si>
@@ -714,9 +1125,30 @@
     <t>http://www.youtube.com/watch?v=y9GKqHNA6i4&amp;t=630s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>12 xe tạm dẫn đầu bình chọn CCA 2026 sau 1 tuần: Xpander bất ngờ vươn lên, Jaecoo J5 thắng lớn, Geely bám sát nút nhiều hạng mục</t>
+  </si>
+  <si>
+    <t>Toyota Innova Cross - Xe gia đình 2026 (Hạng 600 triệu - 1 tỷ đồng) Toyota Innova Cross đang tạm dẫn đầu nhóm xe gia đình 600 triệu - 1 tỷ đồng với 18.955 lượt bình chọn [...] Sự an toàn cũng được chú trọng với gói Toyota Safety Sense có mặt trên phi</t>
+  </si>
+  <si>
+    <t>https://doanhnhanngaynay.com/12-xe-tam-dan-dau-binh-chon-cca-2026-sau-1-tuan-xpander-bat-ngo-vuon-len-jaecoo-j5-thang-lon-geely-bam-sat-nut-nhieu-hang-muc-a316636.html</t>
+  </si>
+  <si>
+    <t>doanhnhanngaynay.com</t>
+  </si>
+  <si>
     <t>03:30</t>
   </si>
   <si>
+    <t>Toyota đang phát triển công nghệ “chụp ảnh bằng ánh mắt\ Toyota đang nghiên cứu công nghệ cho phép chiếc xe tự ghi lại hình ảnh mà tài xế đang quan tâm bằng mắt, mà người lái không cần sử dụng điện thoại khi lái xe</t>
+  </si>
+  <si>
+    <t>https://khoahocdoisong.vn/ra-mat-royal-enfield-himalayan-411-gia-mem-tro-lai-voi-dong-co-443cc-post2149116456.html</t>
+  </si>
+  <si>
+    <t>khoahocdoisong.vn</t>
+  </si>
+  <si>
     <t>✅Tiếp đà giảm sâu| Khuyến mại Toyota Yaris Cross 2026 mới nhất 16/09 lăn bánh chi tiết</t>
   </si>
   <si>
@@ -771,6 +1203,30 @@
     <t>https://www.tiktok.com/@wk.estetica.aut/video/7685704638103833877</t>
   </si>
   <si>
+    <t>03:18</t>
+  </si>
+  <si>
+    <t>automotivecitadel</t>
+  </si>
+  <si>
+    <t>Toyota Corolla DX 1980 ❤️ For Sale Soon at The Automotive Citadel #automotivecitadel #toyotacorolla #80scorolla #toyotaclassic #jdm</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@automotivecitadel/video/7685704494021184800</t>
+  </si>
+  <si>
+    <t>03:17</t>
+  </si>
+  <si>
+    <t>ten49crew</t>
+  </si>
+  <si>
+    <t>Toyota for life💪🏼😍 #toyotatacoma # toyota #4thgen #newtruck #toyotalife</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@ten49crew/video/7685704224415436063</t>
+  </si>
+  <si>
     <t>03:14</t>
   </si>
   <si>
@@ -798,6 +1254,21 @@
     <t>http://www.youtube.com/watch?v=i8_Ewyf-wpI&amp;t=6s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>03:06</t>
+  </si>
+  <si>
+    <t>Android Box Toyota Fortuner</t>
+  </si>
+  <si>
+    <t>Android Box Toyota Fortuner: - Biến màn hình zin thành màn hình Android - Tích hợp bản đồ dẫn đường thông minh - Kho giải trí đa dạng ngay trên màn hình zin - Điều khiển giọng nói thông minh - Cấu hình mạnh mẽ, vận hành mượt mà</t>
+  </si>
+  <si>
+    <t>https://thienauto.com/product/android-box-toyota-fortuner</t>
+  </si>
+  <si>
+    <t>thienauto.com</t>
+  </si>
+  <si>
     <t>02:59</t>
   </si>
   <si>
@@ -831,12 +1302,6 @@
     <t>02:42</t>
   </si>
   <si>
-    <t>facebook.com</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
     <t>CẬP NHẬT GIÁ XE Ô TÔ CŨ CHỈ TỪ 39 TRIỆU - PHÚC VIỆT AUTO #phucvietautoq12</t>
   </si>
   <si>
@@ -849,6 +1314,15 @@
     <t>02:39</t>
   </si>
   <si>
+    <t>eagletdavinson</t>
+  </si>
+  <si>
+    <t>🚘 TOYOTA YARIS CROSS HYBRID — FOR SALE 🇬🇧 🔥 £14,500 🔥 20,000 miles on the clock Clean, stylish and economical Toyota Yaris Cross Hybrid now available for sale [...] ✅ Hybrid engine ✅ Automatic ✅ Beautiful dark grey colour ✅ Clean interior</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@eagletdavinson/video/7685694461690596628</t>
+  </si>
+  <si>
     <t>qhuy.thanglongcars</t>
   </si>
   <si>
@@ -873,6 +1347,18 @@
     <t>tienphong.vn</t>
   </si>
   <si>
+    <t>02:31</t>
+  </si>
+  <si>
+    <t>nrly.car</t>
+  </si>
+  <si>
+    <t>Older model Camry – Special Price # Toyota #Camry #UsedCar #CarExport #LowPriceCar</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@nrly.car/video/7685692234116697352</t>
+  </si>
+  <si>
     <t>02:30</t>
   </si>
   <si>
@@ -942,15 +1428,15 @@
     <t>https://www.sortiraparis.com/vi/tin-tuc/o-paris/articles/352175-disneyland-paris-khi-nao-crush-s-coaster-se-duoc-mo-cua-tro-lai-tai-disney-adventure-world</t>
   </si>
   <si>
-    <t>sortiraparis.com</t>
-  </si>
-  <si>
     <t>02:13</t>
   </si>
   <si>
     <t>Tweet-ID: 2099788668718207158</t>
   </si>
   <si>
+    <t>02:12</t>
+  </si>
+  <si>
     <t>02:10</t>
   </si>
   <si>
@@ -963,6 +1449,18 @@
     <t>http://www.youtube.com/watch?v=viLwxNMJFCw&amp;t=354s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>belinify.yks</t>
+  </si>
+  <si>
+    <t>@coachify.yks indirim kodum BELIN5 #yks # tyt #ayt #yks2027</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@belinify.yks/video/7685685536366890261</t>
+  </si>
+  <si>
     <t>02:03</t>
   </si>
   <si>
@@ -990,6 +1488,9 @@
     <t>http://www.youtube.com/watch?v=1_V90mJ7rNM&amp;t=42s&amp;cc_load_policy=1</t>
   </si>
   <si>
+    <t>01:58</t>
+  </si>
+  <si>
     <t>01:53</t>
   </si>
   <si>
@@ -1035,6 +1536,21 @@
     <t>congluan.vn</t>
   </si>
   <si>
+    <t>01:39</t>
+  </si>
+  <si>
+    <t>Bán vượt Mitsubishi Xpander, Toyota Innova Cross dẫn đầu nhóm MPV chạy xăng tháng 8/2026</t>
+  </si>
+  <si>
+    <t>Đáng chú ý, Mitsubishi Xpander không còn giữ vị trí số một khi Toyota Innova Cross vươn lên dẫn đầu bảng xếp hạng [...] [...]Trong khi đó, Toyota Innova Cross là mẫu xe có mức giảm thấp nhất trong nhóm dẫn đầu [...] [...] Doanh số tháng 8 đạt 829 xe,</t>
+  </si>
+  <si>
+    <t>https://thethao247.vn/419-ban-vuot-mitsubishi-xpander-toyota-innova-cross-dan-dau-nhom-mpv-chay-xang-thang-8-2026-c191-d436217.html</t>
+  </si>
+  <si>
+    <t>thethao247.vn</t>
+  </si>
+  <si>
     <t>01:34</t>
   </si>
   <si>
@@ -1062,6 +1578,33 @@
     <t>tapchikinhtetaichinh.vn</t>
   </si>
   <si>
+    <t>01:26</t>
+  </si>
+  <si>
+    <t>rc_worlds</t>
+  </si>
+  <si>
+    <t>[...] a custom widebody kit, carbon-fiber aero, aggressive bumpers, red projector headlights, deep-dish wheels, low stance, spoiler and more! 🖤❤️ From stock SUV to a head-turning modified beast — this Raize build takes it to another level! 🚀 Like 👍 |</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@rc_worlds/video/7685675603130912020</t>
+  </si>
+  <si>
+    <t>01:22</t>
+  </si>
+  <si>
+    <t>Sedan cỡ B lao dốc trong tháng 8, Honda City giảm hơn 70% doanh số</t>
+  </si>
+  <si>
+    <t>Honda City giảm mạnh nhất, trong khi Toyota Vios vươn lên vị trí dẫn đầu phân khúc [...] Ảnh minh họa.Honda City giảm 73%, Toyota Vios lên dẫn đầuToyota Vios bán được 656 xe trong tháng 8, giảm 32,2% so với mức 968 xe của tháng 7 [...] [...] năm cũng</t>
+  </si>
+  <si>
+    <t>https://docnhanh.vn/oto-xe-may/sedan-co-b-lao-doc-trong-thang-8-honda-city-giam-hon-70-doanh-so-tintuc1051601</t>
+  </si>
+  <si>
+    <t>docnhanh.vn</t>
+  </si>
+  <si>
     <t>01:20</t>
   </si>
   <si>
@@ -1098,6 +1641,18 @@
     <t>https://www.tiktok.com/@hardyclassiccataloq/video/7685672893790915860</t>
   </si>
   <si>
+    <t>01:12</t>
+  </si>
+  <si>
+    <t>thechardieb</t>
+  </si>
+  <si>
+    <t>Buying myself a toy after surviving Hi Bye, Mama! The Grave of the Fireflies, and Scarlet Heart Ryeo</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@thechardieb/video/7685672029126708488</t>
+  </si>
+  <si>
     <t>01:08</t>
   </si>
   <si>
@@ -1110,6 +1665,21 @@
     <t>https://www.tiktok.com/@evw716/video/7685670929762077955</t>
   </si>
   <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>5 mẫu sedan bán nhiều nhất tháng 8/2026, Vios dẫn đầu, Mazda2 gây bất ngờ</t>
+  </si>
+  <si>
+    <t>Trang chủ Ô tô Thứ Ba, ngày 15/09/2026 07:37 AM (GMT+7) Toyota Vios lấy lại ngôi đầu phân khúc sau khi bị Honda City vượt mặt trong tháng 7 [...] Theo Hà Nhi ([Tên nguồn]) Nguồn: [Link nguồn]-15/09/2026 06:31 AM (GMT+7) Toyota Vios Xem thêm</t>
+  </si>
+  <si>
+    <t>https://www.24h.com.vn/o-to/5-mau-sedan-ban-nhieu-nhat-thang-8-2026-vios-dan-dau-mazda2-gay-bat-ngo-c747a1794772.html</t>
+  </si>
+  <si>
+    <t>24h.com.vn</t>
+  </si>
+  <si>
     <t>00:53</t>
   </si>
   <si>
@@ -1122,6 +1692,33 @@
     <t>https://www.tiktok.com/@citytoysygn/video/7685667115952606472</t>
   </si>
   <si>
+    <t>00:48</t>
+  </si>
+  <si>
+    <t>200 doanh nghiệp nộp ngân sách gần 1 triệu tỷ, sao thiếu Samsung, Intel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[...] sách 148.773 PVNSố nộp ngân sách 90.991 ViettelSố nộp ngân sách 42.290 PetrolimexSố nộp ngân sách 30.575 Heineken Việt NamSố nộp ngân sách 27.000 Toyota Việt NamSố nộp ngân sách 26.000 SunshineSố nộp ngân sách 24.045 TKVSố nộp ngân sách 24.031 </t>
+  </si>
+  <si>
+    <t>https://znews.vn/200-doanh-nghiep-nop-ngan-sach-gan-1-trieu-ty-sao-thieu-samsung-intel-post1683471.html</t>
+  </si>
+  <si>
+    <t>znews.vn</t>
+  </si>
+  <si>
+    <t>00:41</t>
+  </si>
+  <si>
+    <t>Top 10 ô tô xăng, dầu bán chạy tháng 8/2026: Xe sedan hoàn toàn vắng bóng</t>
+  </si>
+  <si>
+    <t>Các vị trí dẫn đầu vẫn thuộc về những mẫu xe quen thuộc như Mazda CX-5 đạt 1.092 chiếc, Toyota Yaris Cross đạt 920 chiếc, Toyota Innova Cross đạt 829 chiếc, Ford Ranger đạt 729 chiếc, Ford Everest đạt 690 chiếc và Kia Seltos đạt 686 chiếc</t>
+  </si>
+  <si>
+    <t>https://www.vietnam.vn/top-10-o-to-xang-dau-ban-chay-thang-8-2026-xe-sedan-hoan-toan-vang-bong</t>
+  </si>
+  <si>
     <t>00:40</t>
   </si>
   <si>
@@ -1167,6 +1764,21 @@
     <t>https://www.tiktok.com/@thanhnamtoyota/video/7685662313248083220</t>
   </si>
   <si>
+    <t>00:31</t>
+  </si>
+  <si>
+    <t>Điều người Việt mong chờ ở bán tải VF Wild</t>
+  </si>
+  <si>
+    <t>Thêm một đại diện bán tải chuẩn bị gia nhập thị trường, đối đầu trực tiếp nhóm bán tải thuần xăng dầu như Ford Ranger, Toyota Hilux, Mitsubishi Triton.. [...] Đây là những gì Toyota Hilux đã được trải nghiệm ở thế hệ mới vừa chính thức trình làng khá</t>
+  </si>
+  <si>
+    <t>https://tech.zingnews.vn/dieu-nguoi-viet-mong-cho-o-ban-tai-vf-wild-post1683138.html</t>
+  </si>
+  <si>
+    <t>tech.zingnews.vn</t>
+  </si>
+  <si>
     <t>00:24</t>
   </si>
   <si>
@@ -1266,13 +1878,13 @@
     <t>All</t>
   </si>
   <si>
-    <t>18.09%</t>
-  </si>
-  <si>
-    <t>7.45%</t>
-  </si>
-  <si>
-    <t>53.19%</t>
+    <t>16.45%</t>
+  </si>
+  <si>
+    <t>5.26%</t>
+  </si>
+  <si>
+    <t>50.66%</t>
   </si>
   <si>
     <t>Number of mentions</t>
@@ -1688,7 +2300,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="true" style="0"/>
@@ -1738,7 +2350,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="B3">
-        <v>358297042101145600</v>
+        <v>358366431550685184</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -1746,91 +2358,91 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4">
-        <v>358297883746963456</v>
+        <v>358342435794952192</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5">
-        <v>358280361643393024</v>
+        <v>358362906561204224</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6">
-        <v>358297518712340480</v>
+        <v>358328125626621952</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7">
-        <v>358288199061127168</v>
+        <v>358328125731479552</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -1838,150 +2450,129 @@
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8">
-        <v>358169910616043520</v>
+        <v>358328125786005504</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9">
-        <v>358267634942291968</v>
+        <v>358313009547890688</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="B10">
-        <v>358292906752143360</v>
+        <v>358313009648553984</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11">
-        <v>358288199119847424</v>
+        <v>358322351013826560</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12">
-        <v>358267051757846528</v>
+        <v>358333033104850944</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1989,83 +2580,68 @@
     </row>
     <row r="13" spans="1:11">
       <c r="B13">
-        <v>358267051829149696</v>
+        <v>358322351101906944</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="B14">
-        <v>358271786476945408</v>
+        <v>358341769924304896</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="B15">
-        <v>358267051887869952</v>
+        <v>358337978336149504</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2073,320 +2649,290 @@
     </row>
     <row r="16" spans="1:11">
       <c r="B16">
-        <v>358288199165984768</v>
+        <v>358337977606340608</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="B17">
-        <v>358280361702113280</v>
+        <v>358337977514065920</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="B18">
-        <v>358267051925618688</v>
+        <v>358297042101145600</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="B19">
-        <v>358267051967561728</v>
+        <v>358297883746963456</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="B20">
-        <v>358298575920287744</v>
+        <v>358333548270247936</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="B21">
-        <v>358298576197111808</v>
+        <v>358326627958067200</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="B22">
-        <v>358280361748250624</v>
+        <v>358322837125201920</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="B23">
-        <v>358267052005310464</v>
+        <v>358280361643393024</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="B24">
-        <v>358236492545445888</v>
+        <v>358322836995178496</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="B25">
-        <v>358267052043059200</v>
+        <v>358368571262287872</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="B26">
-        <v>358236492629331968</v>
+        <v>358297518712340480</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>82</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="B27">
-        <v>358250939204812800</v>
+        <v>358288199061127168</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2394,48 +2940,57 @@
     </row>
     <row r="28" spans="1:11">
       <c r="B28">
-        <v>358296604668674048</v>
+        <v>358333033176154112</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="B29">
-        <v>358237389203771392</v>
+        <v>358169910616043520</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" t="s">
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2443,126 +2998,126 @@
     </row>
     <row r="30" spans="1:11">
       <c r="B30">
-        <v>358237389300240384</v>
+        <v>358311453075296256</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="B31">
-        <v>358280361827942400</v>
+        <v>358319325687398400</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="B32">
-        <v>358250939284504576</v>
+        <v>358267634942291968</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="B33">
-        <v>358288199220510720</v>
+        <v>358292906752143360</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>99</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="B34">
-        <v>358222277600423936</v>
+        <v>358288199119847424</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>114</v>
+      </c>
+      <c r="E34" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2570,115 +3125,106 @@
     </row>
     <row r="35" spans="1:11">
       <c r="B35">
-        <v>358288936444899328</v>
+        <v>358357585188929536</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="B36">
-        <v>358275566874443776</v>
+        <v>358357585285398528</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="B37">
-        <v>358244889420414976</v>
+        <v>358357585339924480</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G37" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="B38">
-        <v>358244889495912448</v>
+        <v>358267051757846528</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E38" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="G38" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2686,109 +3232,112 @@
     </row>
     <row r="39" spans="1:11">
       <c r="B39">
-        <v>358244889529466880</v>
+        <v>358357585398644736</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G39" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="B40">
-        <v>358249918005035008</v>
+        <v>358267051829149696</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F40" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G40" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="B41">
-        <v>358222277696892928</v>
+        <v>358271786476945408</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>142</v>
+      </c>
+      <c r="E41" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" t="s">
+        <v>144</v>
       </c>
       <c r="G41" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="B42">
-        <v>358244889575604224</v>
+        <v>358267051887869952</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2796,22 +3345,28 @@
     </row>
     <row r="43" spans="1:11">
       <c r="B43">
-        <v>358222277743030272</v>
+        <v>358315539057131520</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>150</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" t="s">
+        <v>152</v>
       </c>
       <c r="G43" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2819,22 +3374,28 @@
     </row>
     <row r="44" spans="1:11">
       <c r="B44">
-        <v>358266005450973184</v>
+        <v>358288199165984768</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>154</v>
+      </c>
+      <c r="E44" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" t="s">
+        <v>156</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2842,22 +3403,28 @@
     </row>
     <row r="45" spans="1:11">
       <c r="B45">
-        <v>358266005400641536</v>
+        <v>358312021713797120</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
       </c>
       <c r="D45" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" t="s">
         <v>159</v>
+      </c>
+      <c r="F45" t="s">
+        <v>160</v>
       </c>
       <c r="G45" t="s">
         <v>161</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2865,7 +3432,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="B46">
-        <v>358266004708581376</v>
+        <v>358280361702113280</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -2873,14 +3440,20 @@
       <c r="D46" t="s">
         <v>162</v>
       </c>
+      <c r="E46" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" t="s">
+        <v>164</v>
+      </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2888,85 +3461,88 @@
     </row>
     <row r="47" spans="1:11">
       <c r="B47">
-        <v>358266004586946560</v>
+        <v>358368571354562560</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>166</v>
+      </c>
+      <c r="E47" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" t="s">
+        <v>168</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="B48">
-        <v>358244889613352960</v>
+        <v>358312022112256000</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E48" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G48" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H48" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="B49">
-        <v>358301187327442944</v>
+        <v>358267051925618688</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>85</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="B50">
-        <v>358207140692860928</v>
+        <v>358267051967561728</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -2974,37 +3550,49 @@
       <c r="D50" t="s">
         <v>174</v>
       </c>
+      <c r="E50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" t="s">
+        <v>178</v>
+      </c>
       <c r="G50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="B51">
-        <v>358207140806107136</v>
+        <v>358298575920287744</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="E51" t="s">
+        <v>180</v>
+      </c>
+      <c r="F51" t="s">
+        <v>181</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -3012,28 +3600,28 @@
     </row>
     <row r="52" spans="1:11">
       <c r="B52">
-        <v>358244889655296000</v>
+        <v>358298576197111808</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E52" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H52" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3041,57 +3629,57 @@
     </row>
     <row r="53" spans="1:11">
       <c r="B53">
-        <v>358244889697239040</v>
+        <v>358280361748250624</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G53" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="B54">
-        <v>358244889734987776</v>
+        <v>358267052005310464</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F54" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G54" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H54" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I54" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3099,86 +3687,77 @@
     </row>
     <row r="55" spans="1:11">
       <c r="B55">
-        <v>358244889768542208</v>
+        <v>358312023064363008</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F55" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H55" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="B56">
-        <v>358244889814679552</v>
+        <v>358236492545445888</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
-      </c>
-      <c r="E56" t="s">
-        <v>191</v>
-      </c>
-      <c r="F56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G56" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="B57">
-        <v>358216927853694976</v>
+        <v>358267052043059200</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="G57" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H57" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="I57" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3186,198 +3765,186 @@
     </row>
     <row r="58" spans="1:11">
       <c r="B58">
-        <v>358244889852428288</v>
+        <v>358236492629331968</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>196</v>
-      </c>
-      <c r="E58" t="s">
-        <v>197</v>
-      </c>
-      <c r="F58" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G58" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="B59">
-        <v>358273736887058432</v>
+        <v>358250939204812800</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E59" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G59" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H59" t="s">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>85</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="B60">
-        <v>358300324127059968</v>
+        <v>358296604668674048</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E60" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F60" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G60" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H60" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="B61">
-        <v>358207140873216000</v>
+        <v>358333033230680064</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+      <c r="E61" t="s">
+        <v>214</v>
+      </c>
+      <c r="F61" t="s">
+        <v>215</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>14</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="B62">
-        <v>358249918088921088</v>
+        <v>358237389203771392</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>211</v>
-      </c>
-      <c r="E62" t="s">
-        <v>212</v>
-      </c>
-      <c r="F62" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G62" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="B63">
-        <v>358244889890177024</v>
+        <v>358330391179939840</v>
       </c>
       <c r="C63" t="s">
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E63" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F63" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G63" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H63" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>28</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="B64">
-        <v>358250939326447616</v>
+        <v>358237389300240384</v>
       </c>
       <c r="C64" t="s">
         <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" t="s">
-        <v>220</v>
-      </c>
-      <c r="F64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H64" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I64" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="B65">
-        <v>358244889932120064</v>
+        <v>358313097800208384</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
@@ -3386,271 +3953,262 @@
         <v>223</v>
       </c>
       <c r="E65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="I65" t="s">
-        <v>28</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="B66">
-        <v>358244889965674496</v>
+        <v>358360998693879809</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F66" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G66" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H66" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>28</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="B67">
-        <v>358244889999228928</v>
+        <v>358280361827942400</v>
       </c>
       <c r="C67" t="s">
         <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F67" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="B68">
-        <v>358250939372584960</v>
+        <v>358312024091967488</v>
       </c>
       <c r="C68" t="s">
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E68" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F68" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G68" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H68" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J68">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="B69">
-        <v>358266312260075520</v>
+        <v>358250939284504576</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
       </c>
       <c r="D69" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E69" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F69" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G69" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="B70">
-        <v>358270094482128896</v>
+        <v>358288199220510720</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E70" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F70" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G70" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="B71">
-        <v>358256454416928768</v>
+        <v>358357585448976384</v>
       </c>
       <c r="C71" t="s">
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E71" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F71" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G71" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="B72">
-        <v>358244890045366272</v>
+        <v>358222277600423936</v>
       </c>
       <c r="C72" t="s">
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>250</v>
-      </c>
-      <c r="E72" t="s">
-        <v>251</v>
-      </c>
-      <c r="F72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H72" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="B73">
-        <v>358254626685915136</v>
+        <v>358312024159076353</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>250</v>
+        <v>255</v>
+      </c>
+      <c r="E73" t="s">
+        <v>256</v>
+      </c>
+      <c r="F73" t="s">
+        <v>257</v>
       </c>
       <c r="G73" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>14</v>
-      </c>
-      <c r="J73">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="B74">
-        <v>358244890083115008</v>
+        <v>358288936444899328</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E74" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F74" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H74" t="s">
-        <v>27</v>
+        <v>263</v>
       </c>
       <c r="I74" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -3658,57 +4216,57 @@
     </row>
     <row r="75" spans="1:11">
       <c r="B75">
-        <v>358244890120863744</v>
+        <v>358275566874443776</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E75" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F75" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G75" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H75" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="B76">
-        <v>358244890158612480</v>
+        <v>358244889420414976</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E76" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F76" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G76" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H76" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -3716,126 +4274,138 @@
     </row>
     <row r="77" spans="1:11">
       <c r="B77">
-        <v>358192028514979840</v>
+        <v>358244889495912448</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>267</v>
+        <v>272</v>
+      </c>
+      <c r="E77" t="s">
+        <v>273</v>
+      </c>
+      <c r="F77" t="s">
+        <v>274</v>
       </c>
       <c r="G77" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="I77" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="B78">
-        <v>358294472632643584</v>
+        <v>358244889529466880</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>269</v>
+        <v>272</v>
+      </c>
+      <c r="E78" t="s">
+        <v>276</v>
+      </c>
+      <c r="F78" t="s">
+        <v>277</v>
+      </c>
+      <c r="G78" t="s">
+        <v>278</v>
       </c>
       <c r="H78" t="s">
-        <v>270</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s">
-        <v>271</v>
+        <v>85</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="B79">
-        <v>358244890192166912</v>
+        <v>358249918005035008</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E79" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F79" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="G79" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="H79" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I79" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="B80">
-        <v>358262517677441024</v>
+        <v>358222277696892928</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>275</v>
-      </c>
-      <c r="E80" t="s">
-        <v>276</v>
-      </c>
-      <c r="F80" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="G80" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="B81">
-        <v>358250991658741760</v>
+        <v>358244889575604224</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E81" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F81" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G81" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H81" t="s">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="I81" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -3843,28 +4413,22 @@
     </row>
     <row r="82" spans="1:11">
       <c r="B82">
-        <v>358244890234109952</v>
+        <v>358222277743030272</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
       </c>
       <c r="D82" t="s">
-        <v>284</v>
-      </c>
-      <c r="E82" t="s">
-        <v>285</v>
-      </c>
-      <c r="F82" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G82" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H82" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I82" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -3872,28 +4436,22 @@
     </row>
     <row r="83" spans="1:11">
       <c r="B83">
-        <v>358244890271858688</v>
+        <v>358266005450973184</v>
       </c>
       <c r="C83" t="s">
         <v>10</v>
       </c>
       <c r="D83" t="s">
-        <v>284</v>
-      </c>
-      <c r="E83" t="s">
-        <v>288</v>
-      </c>
-      <c r="F83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G83" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I83" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -3901,57 +4459,45 @@
     </row>
     <row r="84" spans="1:11">
       <c r="B84">
-        <v>358232428495552512</v>
+        <v>358266005400641536</v>
       </c>
       <c r="C84" t="s">
         <v>10</v>
       </c>
       <c r="D84" t="s">
-        <v>291</v>
-      </c>
-      <c r="E84" t="s">
+        <v>290</v>
+      </c>
+      <c r="G84" t="s">
         <v>292</v>
       </c>
-      <c r="F84" t="s">
-        <v>293</v>
-      </c>
-      <c r="G84" t="s">
-        <v>294</v>
-      </c>
       <c r="H84" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="B85">
-        <v>358250991537106944</v>
+        <v>358266004708581376</v>
       </c>
       <c r="C85" t="s">
         <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>295</v>
-      </c>
-      <c r="E85" t="s">
-        <v>296</v>
-      </c>
-      <c r="F85" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G85" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H85" t="s">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -3959,28 +4505,22 @@
     </row>
     <row r="86" spans="1:11">
       <c r="B86">
-        <v>358244890305413120</v>
+        <v>358266004586946560</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
       </c>
       <c r="D86" t="s">
-        <v>300</v>
-      </c>
-      <c r="E86" t="s">
-        <v>301</v>
-      </c>
-      <c r="F86" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G86" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="H86" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -3988,28 +4528,28 @@
     </row>
     <row r="87" spans="1:11">
       <c r="B87">
-        <v>358236461264302080</v>
+        <v>358244889613352960</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
       </c>
       <c r="D87" t="s">
+        <v>297</v>
+      </c>
+      <c r="E87" t="s">
+        <v>298</v>
+      </c>
+      <c r="F87" t="s">
+        <v>299</v>
+      </c>
+      <c r="G87" t="s">
         <v>300</v>
       </c>
-      <c r="E87" t="s">
-        <v>304</v>
-      </c>
-      <c r="F87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G87" t="s">
-        <v>306</v>
-      </c>
       <c r="H87" t="s">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="I87" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -4017,167 +4557,146 @@
     </row>
     <row r="88" spans="1:11">
       <c r="B88">
-        <v>358192028594671616</v>
+        <v>358301187327442944</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
       </c>
       <c r="D88" t="s">
-        <v>308</v>
+        <v>301</v>
+      </c>
+      <c r="E88" t="s">
+        <v>302</v>
+      </c>
+      <c r="F88" t="s">
+        <v>303</v>
       </c>
       <c r="G88" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J88">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="B89">
-        <v>358244890351550464</v>
+        <v>358207140692860928</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>310</v>
-      </c>
-      <c r="E89" t="s">
-        <v>311</v>
-      </c>
-      <c r="F89" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G89" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="H89" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I89" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="B90">
-        <v>358119333278371840</v>
+        <v>358207140806107136</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>314</v>
-      </c>
-      <c r="E90" t="s">
-        <v>315</v>
-      </c>
-      <c r="F90" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="G90" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="H90" t="s">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="B91">
-        <v>358244890393493504</v>
+        <v>358339092599091200</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
       </c>
       <c r="D91" t="s">
-        <v>319</v>
-      </c>
-      <c r="E91" t="s">
-        <v>320</v>
-      </c>
-      <c r="F91" t="s">
-        <v>321</v>
-      </c>
-      <c r="G91" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="H91" t="s">
-        <v>27</v>
+        <v>309</v>
       </c>
       <c r="I91" t="s">
-        <v>28</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="B92">
-        <v>358244890435436544</v>
+        <v>358333033272623104</v>
       </c>
       <c r="C92" t="s">
         <v>10</v>
       </c>
       <c r="D92" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E92" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="G92" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H92" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I92" t="s">
-        <v>28</v>
-      </c>
-      <c r="J92">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="B93">
-        <v>358244890473185280</v>
+        <v>358244889655296000</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E93" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F93" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="G93" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H93" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I93" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -4185,28 +4704,28 @@
     </row>
     <row r="94" spans="1:11">
       <c r="B94">
-        <v>358216927891443712</v>
+        <v>358244889697239040</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="E94" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="F94" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="G94" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="H94" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="I94" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -4214,28 +4733,28 @@
     </row>
     <row r="95" spans="1:11">
       <c r="B95">
-        <v>358239620246355968</v>
+        <v>358244889734987776</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="E95" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="F95" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="G95" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="H95" t="s">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="I95" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -4243,28 +4762,28 @@
     </row>
     <row r="96" spans="1:11">
       <c r="B96">
-        <v>358270094570209280</v>
+        <v>358244889768542208</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="E96" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="F96" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="G96" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -4272,144 +4791,144 @@
     </row>
     <row r="97" spans="1:11">
       <c r="B97">
-        <v>358216927790780416</v>
+        <v>358244889814679552</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="E97" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="F97" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="G97" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="H97" t="s">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="I97" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="B98">
-        <v>358177795999842304</v>
+        <v>358216927853694976</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="E98" t="s">
-        <v>348</v>
+        <v>95</v>
       </c>
       <c r="F98" t="s">
-        <v>349</v>
+        <v>96</v>
       </c>
       <c r="G98" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="I98" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="B99">
-        <v>358224959211880448</v>
+        <v>358244889852428288</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="E99" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="F99" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="G99" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I99" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="B100">
-        <v>358253650407112704</v>
+        <v>358273736887058432</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="E100" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F100" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="G100" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="B101">
-        <v>358224959312543744</v>
+        <v>358300324127059968</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="E101" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="F101" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="G101" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="I101" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -4417,28 +4936,22 @@
     </row>
     <row r="102" spans="1:11">
       <c r="B102">
-        <v>358249918139252736</v>
+        <v>358207140873216000</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
-      </c>
-      <c r="E102" t="s">
-        <v>364</v>
-      </c>
-      <c r="F102" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="G102" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="H102" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -4446,115 +4959,115 @@
     </row>
     <row r="103" spans="1:11">
       <c r="B103">
-        <v>358171178126311424</v>
+        <v>358249918088921088</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="E103" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="F103" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="G103" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="H103" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I103" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="B104">
-        <v>358244890506739712</v>
+        <v>358244889890177024</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E104" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="F104" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="G104" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="H104" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I104" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="B105">
-        <v>358244890552877056</v>
+        <v>358250939326447616</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="E105" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="F105" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="G105" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="H105" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I105" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="B106">
-        <v>358235964193193984</v>
+        <v>358244889932120064</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="E106" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="F106" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="G106" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H106" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I106" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -4562,106 +5075,112 @@
     </row>
     <row r="107" spans="1:11">
       <c r="B107">
-        <v>358161699150249984</v>
+        <v>358244889965674496</v>
       </c>
       <c r="C107" t="s">
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>382</v>
+        <v>364</v>
+      </c>
+      <c r="E107" t="s">
+        <v>365</v>
+      </c>
+      <c r="F107" t="s">
+        <v>366</v>
       </c>
       <c r="G107" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="I107" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="B108">
-        <v>358297292572581888</v>
+        <v>358310812785344512</v>
       </c>
       <c r="C108" t="s">
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="E108" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="F108" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="G108" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="H108" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="I108" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="B109">
-        <v>358289023610961922</v>
+        <v>358360616794181632</v>
       </c>
       <c r="C109" t="s">
         <v>10</v>
       </c>
       <c r="D109" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="E109" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
       <c r="F109" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="G109" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="H109" t="s">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="I109" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="B110">
-        <v>358171178201808896</v>
+        <v>358244889999228928</v>
       </c>
       <c r="C110" t="s">
         <v>10</v>
       </c>
       <c r="D110" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="E110" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="F110" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="G110" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="H110" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I110" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -4669,88 +5188,1715 @@
     </row>
     <row r="111" spans="1:11">
       <c r="B111">
-        <v>358169910754455552</v>
+        <v>358250939372584960</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
       </c>
       <c r="D111" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="E111" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="F111" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="G111" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="H111" t="s">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="I111" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="B112">
-        <v>358169910842535936</v>
+        <v>358266312260075520</v>
       </c>
       <c r="C112" t="s">
         <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="E112" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="F112" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="G112" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="H112" t="s">
-        <v>406</v>
+        <v>15</v>
       </c>
       <c r="I112" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="B113">
+        <v>358270094482128896</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="s">
+        <v>386</v>
+      </c>
+      <c r="E113" t="s">
+        <v>387</v>
+      </c>
+      <c r="F113" t="s">
+        <v>388</v>
+      </c>
+      <c r="G113" t="s">
+        <v>389</v>
+      </c>
+      <c r="H113" t="s">
+        <v>15</v>
+      </c>
+      <c r="I113" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="B114">
+        <v>358256454416928768</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" t="s">
+        <v>390</v>
+      </c>
+      <c r="E114" t="s">
+        <v>391</v>
+      </c>
+      <c r="F114" t="s">
+        <v>392</v>
+      </c>
+      <c r="G114" t="s">
+        <v>393</v>
+      </c>
+      <c r="H114" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="B115">
+        <v>358333033314566144</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>394</v>
+      </c>
+      <c r="E115" t="s">
+        <v>395</v>
+      </c>
+      <c r="F115" t="s">
+        <v>396</v>
+      </c>
+      <c r="G115" t="s">
+        <v>397</v>
+      </c>
+      <c r="H115" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="B116">
+        <v>358357585495113728</v>
+      </c>
+      <c r="C116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" t="s">
+        <v>398</v>
+      </c>
+      <c r="E116" t="s">
+        <v>399</v>
+      </c>
+      <c r="F116" t="s">
+        <v>400</v>
+      </c>
+      <c r="G116" t="s">
+        <v>401</v>
+      </c>
+      <c r="H116" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="B117">
+        <v>358244890045366272</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" t="s">
+        <v>402</v>
+      </c>
+      <c r="E117" t="s">
+        <v>403</v>
+      </c>
+      <c r="F117" t="s">
+        <v>404</v>
+      </c>
+      <c r="G117" t="s">
+        <v>405</v>
+      </c>
+      <c r="H117" t="s">
+        <v>84</v>
+      </c>
+      <c r="I117" t="s">
+        <v>85</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="B118">
+        <v>358254626685915136</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" t="s">
+        <v>402</v>
+      </c>
+      <c r="G118" t="s">
+        <v>406</v>
+      </c>
+      <c r="H118" t="s">
+        <v>19</v>
+      </c>
+      <c r="I118" t="s">
+        <v>20</v>
+      </c>
+      <c r="J118">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="B119">
+        <v>358244890083115008</v>
+      </c>
+      <c r="C119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" t="s">
+        <v>407</v>
+      </c>
+      <c r="E119" t="s">
+        <v>408</v>
+      </c>
+      <c r="F119" t="s">
+        <v>409</v>
+      </c>
+      <c r="G119" t="s">
+        <v>410</v>
+      </c>
+      <c r="H119" t="s">
+        <v>84</v>
+      </c>
+      <c r="I119" t="s">
+        <v>85</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="B120">
+        <v>358364835362123776</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" t="s">
+        <v>411</v>
+      </c>
+      <c r="E120" t="s">
+        <v>412</v>
+      </c>
+      <c r="F120" t="s">
+        <v>413</v>
+      </c>
+      <c r="G120" t="s">
+        <v>414</v>
+      </c>
+      <c r="H120" t="s">
+        <v>415</v>
+      </c>
+      <c r="I120" t="s">
+        <v>99</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="B121">
+        <v>358244890120863744</v>
+      </c>
+      <c r="C121" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" t="s">
+        <v>416</v>
+      </c>
+      <c r="E121" t="s">
+        <v>417</v>
+      </c>
+      <c r="F121" t="s">
+        <v>418</v>
+      </c>
+      <c r="G121" t="s">
+        <v>419</v>
+      </c>
+      <c r="H121" t="s">
+        <v>84</v>
+      </c>
+      <c r="I121" t="s">
+        <v>85</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="B122">
+        <v>358244890158612480</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" t="s">
+        <v>420</v>
+      </c>
+      <c r="E122" t="s">
+        <v>421</v>
+      </c>
+      <c r="F122" t="s">
+        <v>422</v>
+      </c>
+      <c r="G122" t="s">
+        <v>423</v>
+      </c>
+      <c r="H122" t="s">
+        <v>84</v>
+      </c>
+      <c r="I122" t="s">
+        <v>85</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="B123">
+        <v>358192028514979840</v>
+      </c>
+      <c r="C123" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" t="s">
+        <v>424</v>
+      </c>
+      <c r="G123" t="s">
+        <v>425</v>
+      </c>
+      <c r="H123" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" t="s">
+        <v>20</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="B124">
+        <v>358294472632643584</v>
+      </c>
+      <c r="C124" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" t="s">
+        <v>426</v>
+      </c>
+      <c r="H124" t="s">
+        <v>309</v>
+      </c>
+      <c r="I124" t="s">
+        <v>310</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="B125">
+        <v>358244890192166912</v>
+      </c>
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>426</v>
+      </c>
+      <c r="E125" t="s">
+        <v>427</v>
+      </c>
+      <c r="F125" t="s">
+        <v>428</v>
+      </c>
+      <c r="G125" t="s">
+        <v>429</v>
+      </c>
+      <c r="H125" t="s">
+        <v>84</v>
+      </c>
+      <c r="I125" t="s">
+        <v>85</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="B126">
+        <v>358312024209408000</v>
+      </c>
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" t="s">
+        <v>430</v>
+      </c>
+      <c r="E126" t="s">
+        <v>431</v>
+      </c>
+      <c r="F126" t="s">
+        <v>432</v>
+      </c>
+      <c r="G126" t="s">
+        <v>433</v>
+      </c>
+      <c r="H126" t="s">
+        <v>15</v>
+      </c>
+      <c r="I126" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="B127">
+        <v>358262517677441024</v>
+      </c>
+      <c r="C127" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" t="s">
+        <v>430</v>
+      </c>
+      <c r="E127" t="s">
+        <v>434</v>
+      </c>
+      <c r="F127" t="s">
+        <v>435</v>
+      </c>
+      <c r="G127" t="s">
+        <v>436</v>
+      </c>
+      <c r="H127" t="s">
+        <v>15</v>
+      </c>
+      <c r="I127" t="s">
+        <v>16</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="B128">
+        <v>358250991658741760</v>
+      </c>
+      <c r="C128" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" t="s">
+        <v>437</v>
+      </c>
+      <c r="E128" t="s">
+        <v>438</v>
+      </c>
+      <c r="F128" t="s">
+        <v>439</v>
+      </c>
+      <c r="G128" t="s">
+        <v>440</v>
+      </c>
+      <c r="H128" t="s">
+        <v>441</v>
+      </c>
+      <c r="I128" t="s">
+        <v>99</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="B129">
+        <v>358357585553833984</v>
+      </c>
+      <c r="C129" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" t="s">
+        <v>442</v>
+      </c>
+      <c r="E129" t="s">
+        <v>443</v>
+      </c>
+      <c r="F129" t="s">
+        <v>444</v>
+      </c>
+      <c r="G129" t="s">
+        <v>445</v>
+      </c>
+      <c r="H129" t="s">
+        <v>15</v>
+      </c>
+      <c r="I129" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="B130">
+        <v>358244890234109952</v>
+      </c>
+      <c r="C130" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" t="s">
+        <v>446</v>
+      </c>
+      <c r="E130" t="s">
+        <v>447</v>
+      </c>
+      <c r="F130" t="s">
+        <v>448</v>
+      </c>
+      <c r="G130" t="s">
+        <v>449</v>
+      </c>
+      <c r="H130" t="s">
+        <v>84</v>
+      </c>
+      <c r="I130" t="s">
+        <v>85</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="B131">
+        <v>358244890271858688</v>
+      </c>
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" t="s">
+        <v>446</v>
+      </c>
+      <c r="E131" t="s">
+        <v>450</v>
+      </c>
+      <c r="F131" t="s">
+        <v>451</v>
+      </c>
+      <c r="G131" t="s">
+        <v>452</v>
+      </c>
+      <c r="H131" t="s">
+        <v>84</v>
+      </c>
+      <c r="I131" t="s">
+        <v>85</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="B132">
+        <v>358232428495552512</v>
+      </c>
+      <c r="C132" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" t="s">
+        <v>454</v>
+      </c>
+      <c r="F132" t="s">
+        <v>455</v>
+      </c>
+      <c r="G132" t="s">
+        <v>456</v>
+      </c>
+      <c r="H132" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" t="s">
+        <v>16</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="B133">
+        <v>358250991537106944</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" t="s">
+        <v>457</v>
+      </c>
+      <c r="E133" t="s">
+        <v>458</v>
+      </c>
+      <c r="F133" t="s">
+        <v>459</v>
+      </c>
+      <c r="G133" t="s">
+        <v>460</v>
+      </c>
+      <c r="H133" t="s">
+        <v>461</v>
+      </c>
+      <c r="I133" t="s">
+        <v>99</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="B134">
+        <v>358244890305413120</v>
+      </c>
+      <c r="C134" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" t="s">
+        <v>462</v>
+      </c>
+      <c r="E134" t="s">
+        <v>463</v>
+      </c>
+      <c r="F134" t="s">
+        <v>464</v>
+      </c>
+      <c r="G134" t="s">
+        <v>465</v>
+      </c>
+      <c r="H134" t="s">
+        <v>84</v>
+      </c>
+      <c r="I134" t="s">
+        <v>85</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="B135">
+        <v>358236461264302080</v>
+      </c>
+      <c r="C135" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" t="s">
+        <v>462</v>
+      </c>
+      <c r="E135" t="s">
+        <v>466</v>
+      </c>
+      <c r="F135" t="s">
+        <v>467</v>
+      </c>
+      <c r="G135" t="s">
+        <v>468</v>
+      </c>
+      <c r="H135" t="s">
+        <v>228</v>
+      </c>
+      <c r="I135" t="s">
+        <v>99</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="B136">
+        <v>358192028594671616</v>
+      </c>
+      <c r="C136" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" t="s">
+        <v>469</v>
+      </c>
+      <c r="G136" t="s">
+        <v>470</v>
+      </c>
+      <c r="H136" t="s">
+        <v>19</v>
+      </c>
+      <c r="I136" t="s">
+        <v>20</v>
+      </c>
+      <c r="J136">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="B137">
+        <v>358350445267202048</v>
+      </c>
+      <c r="C137" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" t="s">
+        <v>471</v>
+      </c>
+      <c r="H137" t="s">
+        <v>309</v>
+      </c>
+      <c r="I137" t="s">
+        <v>310</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="B138">
+        <v>358244890351550464</v>
+      </c>
+      <c r="C138" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" t="s">
+        <v>472</v>
+      </c>
+      <c r="E138" t="s">
+        <v>473</v>
+      </c>
+      <c r="F138" t="s">
+        <v>474</v>
+      </c>
+      <c r="G138" t="s">
+        <v>475</v>
+      </c>
+      <c r="H138" t="s">
+        <v>84</v>
+      </c>
+      <c r="I138" t="s">
+        <v>85</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="B139">
+        <v>358342954168926208</v>
+      </c>
+      <c r="C139" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" t="s">
+        <v>476</v>
+      </c>
+      <c r="E139" t="s">
+        <v>477</v>
+      </c>
+      <c r="F139" t="s">
+        <v>478</v>
+      </c>
+      <c r="G139" t="s">
+        <v>479</v>
+      </c>
+      <c r="H139" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="B140">
+        <v>358119333278371840</v>
+      </c>
+      <c r="C140" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" t="s">
+        <v>480</v>
+      </c>
+      <c r="E140" t="s">
+        <v>481</v>
+      </c>
+      <c r="F140" t="s">
+        <v>482</v>
+      </c>
+      <c r="G140" t="s">
+        <v>483</v>
+      </c>
+      <c r="H140" t="s">
+        <v>484</v>
+      </c>
+      <c r="I140" t="s">
+        <v>99</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="B141">
+        <v>358244890393493504</v>
+      </c>
+      <c r="C141" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" t="s">
+        <v>485</v>
+      </c>
+      <c r="E141" t="s">
+        <v>486</v>
+      </c>
+      <c r="F141" t="s">
+        <v>487</v>
+      </c>
+      <c r="G141" t="s">
+        <v>488</v>
+      </c>
+      <c r="H141" t="s">
+        <v>84</v>
+      </c>
+      <c r="I141" t="s">
+        <v>85</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="B142">
+        <v>358339092653617152</v>
+      </c>
+      <c r="C142" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" t="s">
+        <v>489</v>
+      </c>
+      <c r="H142" t="s">
+        <v>309</v>
+      </c>
+      <c r="I142" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="B143">
+        <v>358244890435436544</v>
+      </c>
+      <c r="C143" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" t="s">
+        <v>490</v>
+      </c>
+      <c r="E143" t="s">
+        <v>491</v>
+      </c>
+      <c r="F143" t="s">
+        <v>492</v>
+      </c>
+      <c r="G143" t="s">
+        <v>493</v>
+      </c>
+      <c r="H143" t="s">
+        <v>84</v>
+      </c>
+      <c r="I143" t="s">
+        <v>85</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="B144">
+        <v>358244890473185280</v>
+      </c>
+      <c r="C144" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" t="s">
+        <v>490</v>
+      </c>
+      <c r="E144" t="s">
+        <v>494</v>
+      </c>
+      <c r="F144" t="s">
+        <v>495</v>
+      </c>
+      <c r="G144" t="s">
+        <v>496</v>
+      </c>
+      <c r="H144" t="s">
+        <v>84</v>
+      </c>
+      <c r="I144" t="s">
+        <v>85</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="B145">
+        <v>358216927891443712</v>
+      </c>
+      <c r="C145" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" t="s">
+        <v>497</v>
+      </c>
+      <c r="E145" t="s">
+        <v>498</v>
+      </c>
+      <c r="F145" t="s">
+        <v>499</v>
+      </c>
+      <c r="G145" t="s">
+        <v>500</v>
+      </c>
+      <c r="H145" t="s">
+        <v>501</v>
+      </c>
+      <c r="I145" t="s">
+        <v>99</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="B146">
+        <v>358239620246355968</v>
+      </c>
+      <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" t="s">
+        <v>497</v>
+      </c>
+      <c r="E146" t="s">
+        <v>498</v>
+      </c>
+      <c r="F146" t="s">
+        <v>502</v>
+      </c>
+      <c r="G146" t="s">
+        <v>503</v>
+      </c>
+      <c r="H146" t="s">
+        <v>504</v>
+      </c>
+      <c r="I146" t="s">
+        <v>99</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="B147">
+        <v>358342075038646272</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147" t="s">
+        <v>505</v>
+      </c>
+      <c r="E147" t="s">
+        <v>506</v>
+      </c>
+      <c r="F147" t="s">
+        <v>507</v>
+      </c>
+      <c r="G147" t="s">
+        <v>508</v>
+      </c>
+      <c r="H147" t="s">
+        <v>509</v>
+      </c>
+      <c r="I147" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="B148">
+        <v>358270094570209280</v>
+      </c>
+      <c r="C148" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" t="s">
+        <v>510</v>
+      </c>
+      <c r="E148" t="s">
+        <v>511</v>
+      </c>
+      <c r="F148" t="s">
+        <v>512</v>
+      </c>
+      <c r="G148" t="s">
+        <v>513</v>
+      </c>
+      <c r="H148" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148" t="s">
+        <v>16</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="B149">
+        <v>358216927790780416</v>
+      </c>
+      <c r="C149" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" t="s">
+        <v>514</v>
+      </c>
+      <c r="E149" t="s">
+        <v>515</v>
+      </c>
+      <c r="F149" t="s">
+        <v>516</v>
+      </c>
+      <c r="G149" t="s">
+        <v>517</v>
+      </c>
+      <c r="H149" t="s">
+        <v>518</v>
+      </c>
+      <c r="I149" t="s">
+        <v>99</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="B150">
+        <v>358357585608359936</v>
+      </c>
+      <c r="C150" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" t="s">
+        <v>519</v>
+      </c>
+      <c r="E150" t="s">
+        <v>520</v>
+      </c>
+      <c r="F150" t="s">
+        <v>521</v>
+      </c>
+      <c r="G150" t="s">
+        <v>522</v>
+      </c>
+      <c r="H150" t="s">
+        <v>15</v>
+      </c>
+      <c r="I150" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="B151">
+        <v>358307514984550400</v>
+      </c>
+      <c r="C151" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" t="s">
+        <v>523</v>
+      </c>
+      <c r="E151" t="s">
+        <v>524</v>
+      </c>
+      <c r="F151" t="s">
+        <v>525</v>
+      </c>
+      <c r="G151" t="s">
+        <v>526</v>
+      </c>
+      <c r="H151" t="s">
+        <v>527</v>
+      </c>
+      <c r="I151" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="B152">
+        <v>358177795999842304</v>
+      </c>
+      <c r="C152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" t="s">
+        <v>528</v>
+      </c>
+      <c r="E152" t="s">
+        <v>529</v>
+      </c>
+      <c r="F152" t="s">
+        <v>530</v>
+      </c>
+      <c r="G152" t="s">
+        <v>531</v>
+      </c>
+      <c r="H152" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" t="s">
+        <v>16</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="B153">
+        <v>358224959211880448</v>
+      </c>
+      <c r="C153" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" t="s">
+        <v>532</v>
+      </c>
+      <c r="E153" t="s">
+        <v>533</v>
+      </c>
+      <c r="F153" t="s">
+        <v>534</v>
+      </c>
+      <c r="G153" t="s">
+        <v>535</v>
+      </c>
+      <c r="H153" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" t="s">
+        <v>16</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="B154">
+        <v>358253650407112704</v>
+      </c>
+      <c r="C154" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154" t="s">
+        <v>536</v>
+      </c>
+      <c r="E154" t="s">
+        <v>537</v>
+      </c>
+      <c r="F154" t="s">
+        <v>538</v>
+      </c>
+      <c r="G154" t="s">
+        <v>539</v>
+      </c>
+      <c r="H154" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" t="s">
+        <v>16</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="B155">
+        <v>358330391087665152</v>
+      </c>
+      <c r="C155" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155" t="s">
+        <v>540</v>
+      </c>
+      <c r="E155" t="s">
+        <v>541</v>
+      </c>
+      <c r="F155" t="s">
+        <v>542</v>
+      </c>
+      <c r="G155" t="s">
+        <v>543</v>
+      </c>
+      <c r="H155" t="s">
+        <v>15</v>
+      </c>
+      <c r="I155" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="B156">
+        <v>358224959312543744</v>
+      </c>
+      <c r="C156" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156" t="s">
+        <v>544</v>
+      </c>
+      <c r="E156" t="s">
+        <v>545</v>
+      </c>
+      <c r="F156" t="s">
+        <v>546</v>
+      </c>
+      <c r="G156" t="s">
+        <v>547</v>
+      </c>
+      <c r="H156" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" t="s">
+        <v>16</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="B157">
+        <v>358307515160711168</v>
+      </c>
+      <c r="C157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157" t="s">
+        <v>548</v>
+      </c>
+      <c r="E157" t="s">
+        <v>549</v>
+      </c>
+      <c r="F157" t="s">
+        <v>550</v>
+      </c>
+      <c r="G157" t="s">
+        <v>551</v>
+      </c>
+      <c r="H157" t="s">
+        <v>552</v>
+      </c>
+      <c r="I157" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="B158">
+        <v>358249918139252736</v>
+      </c>
+      <c r="C158" t="s">
+        <v>10</v>
+      </c>
+      <c r="D158" t="s">
+        <v>553</v>
+      </c>
+      <c r="E158" t="s">
+        <v>554</v>
+      </c>
+      <c r="F158" t="s">
+        <v>555</v>
+      </c>
+      <c r="G158" t="s">
+        <v>556</v>
+      </c>
+      <c r="H158" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" t="s">
+        <v>16</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="B159">
+        <v>358360616869679104</v>
+      </c>
+      <c r="C159" t="s">
+        <v>10</v>
+      </c>
+      <c r="D159" t="s">
+        <v>557</v>
+      </c>
+      <c r="E159" t="s">
+        <v>558</v>
+      </c>
+      <c r="F159" t="s">
+        <v>559</v>
+      </c>
+      <c r="G159" t="s">
+        <v>560</v>
+      </c>
+      <c r="H159" t="s">
+        <v>561</v>
+      </c>
+      <c r="I159" t="s">
+        <v>99</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="B160">
+        <v>358307515244597248</v>
+      </c>
+      <c r="C160" t="s">
+        <v>10</v>
+      </c>
+      <c r="D160" t="s">
+        <v>562</v>
+      </c>
+      <c r="E160" t="s">
+        <v>563</v>
+      </c>
+      <c r="F160" t="s">
+        <v>564</v>
+      </c>
+      <c r="G160" t="s">
+        <v>565</v>
+      </c>
+      <c r="H160" t="s">
+        <v>501</v>
+      </c>
+      <c r="I160" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="B161">
+        <v>358171178126311424</v>
+      </c>
+      <c r="C161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" t="s">
+        <v>566</v>
+      </c>
+      <c r="E161" t="s">
+        <v>567</v>
+      </c>
+      <c r="F161" t="s">
+        <v>568</v>
+      </c>
+      <c r="G161" t="s">
+        <v>569</v>
+      </c>
+      <c r="H161" t="s">
+        <v>15</v>
+      </c>
+      <c r="I161" t="s">
+        <v>16</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="B162">
+        <v>358244890506739712</v>
+      </c>
+      <c r="C162" t="s">
+        <v>10</v>
+      </c>
+      <c r="D162" t="s">
+        <v>566</v>
+      </c>
+      <c r="E162" t="s">
+        <v>570</v>
+      </c>
+      <c r="F162" t="s">
+        <v>571</v>
+      </c>
+      <c r="G162" t="s">
+        <v>572</v>
+      </c>
+      <c r="H162" t="s">
+        <v>84</v>
+      </c>
+      <c r="I162" t="s">
+        <v>85</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="B163">
+        <v>358244890552877056</v>
+      </c>
+      <c r="C163" t="s">
+        <v>10</v>
+      </c>
+      <c r="D163" t="s">
+        <v>573</v>
+      </c>
+      <c r="E163" t="s">
+        <v>574</v>
+      </c>
+      <c r="F163" t="s">
+        <v>575</v>
+      </c>
+      <c r="G163" t="s">
+        <v>576</v>
+      </c>
+      <c r="H163" t="s">
+        <v>84</v>
+      </c>
+      <c r="I163" t="s">
+        <v>85</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="B164">
+        <v>358235964193193984</v>
+      </c>
+      <c r="C164" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164" t="s">
+        <v>577</v>
+      </c>
+      <c r="E164" t="s">
+        <v>578</v>
+      </c>
+      <c r="F164" t="s">
+        <v>579</v>
+      </c>
+      <c r="G164" t="s">
+        <v>580</v>
+      </c>
+      <c r="H164" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" t="s">
+        <v>16</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="B165">
+        <v>358353000814678016</v>
+      </c>
+      <c r="C165" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" t="s">
+        <v>581</v>
+      </c>
+      <c r="E165" t="s">
+        <v>582</v>
+      </c>
+      <c r="F165" t="s">
+        <v>583</v>
+      </c>
+      <c r="G165" t="s">
+        <v>584</v>
+      </c>
+      <c r="H165" t="s">
+        <v>585</v>
+      </c>
+      <c r="I165" t="s">
+        <v>99</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="B166">
+        <v>358161699150249984</v>
+      </c>
+      <c r="C166" t="s">
+        <v>10</v>
+      </c>
+      <c r="D166" t="s">
+        <v>586</v>
+      </c>
+      <c r="G166" t="s">
+        <v>587</v>
+      </c>
+      <c r="H166" t="s">
+        <v>19</v>
+      </c>
+      <c r="I166" t="s">
+        <v>20</v>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="B167">
+        <v>358297292572581888</v>
+      </c>
+      <c r="C167" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" t="s">
+        <v>588</v>
+      </c>
+      <c r="E167" t="s">
+        <v>589</v>
+      </c>
+      <c r="F167" t="s">
+        <v>590</v>
+      </c>
+      <c r="G167" t="s">
+        <v>591</v>
+      </c>
+      <c r="H167" t="s">
+        <v>592</v>
+      </c>
+      <c r="I167" t="s">
+        <v>99</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="B168">
+        <v>358289023610961922</v>
+      </c>
+      <c r="C168" t="s">
+        <v>10</v>
+      </c>
+      <c r="D168" t="s">
+        <v>593</v>
+      </c>
+      <c r="E168" t="s">
+        <v>594</v>
+      </c>
+      <c r="F168" t="s">
+        <v>595</v>
+      </c>
+      <c r="G168" t="s">
+        <v>596</v>
+      </c>
+      <c r="H168" t="s">
+        <v>15</v>
+      </c>
+      <c r="I168" t="s">
+        <v>16</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="B169">
+        <v>358171178201808896</v>
+      </c>
+      <c r="C169" t="s">
+        <v>10</v>
+      </c>
+      <c r="D169" t="s">
+        <v>597</v>
+      </c>
+      <c r="E169" t="s">
+        <v>598</v>
+      </c>
+      <c r="F169" t="s">
+        <v>599</v>
+      </c>
+      <c r="G169" t="s">
+        <v>600</v>
+      </c>
+      <c r="H169" t="s">
+        <v>15</v>
+      </c>
+      <c r="I169" t="s">
+        <v>16</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="B170">
+        <v>358169910754455552</v>
+      </c>
+      <c r="C170" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170" t="s">
+        <v>601</v>
+      </c>
+      <c r="E170" t="s">
+        <v>602</v>
+      </c>
+      <c r="F170" t="s">
+        <v>603</v>
+      </c>
+      <c r="G170" t="s">
+        <v>604</v>
+      </c>
+      <c r="H170" t="s">
+        <v>605</v>
+      </c>
+      <c r="I170" t="s">
+        <v>99</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="B171">
+        <v>358169910842535936</v>
+      </c>
+      <c r="C171" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171" t="s">
+        <v>606</v>
+      </c>
+      <c r="E171" t="s">
+        <v>607</v>
+      </c>
+      <c r="F171" t="s">
+        <v>608</v>
+      </c>
+      <c r="G171" t="s">
+        <v>609</v>
+      </c>
+      <c r="H171" t="s">
+        <v>610</v>
+      </c>
+      <c r="I171" t="s">
+        <v>99</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="B172">
         <v>358159134354321408</v>
       </c>
-      <c r="C113" t="s">
-        <v>10</v>
-      </c>
-      <c r="D113" t="s">
-        <v>407</v>
-      </c>
-      <c r="E113" t="s">
-        <v>408</v>
-      </c>
-      <c r="F113" t="s">
-        <v>409</v>
-      </c>
-      <c r="G113" t="s">
-        <v>410</v>
-      </c>
-      <c r="H113" t="s">
-        <v>27</v>
-      </c>
-      <c r="I113" t="s">
-        <v>28</v>
-      </c>
-      <c r="J113">
+      <c r="C172" t="s">
+        <v>10</v>
+      </c>
+      <c r="D172" t="s">
+        <v>611</v>
+      </c>
+      <c r="E172" t="s">
+        <v>612</v>
+      </c>
+      <c r="F172" t="s">
+        <v>613</v>
+      </c>
+      <c r="G172" t="s">
+        <v>614</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172" t="s">
+        <v>85</v>
+      </c>
+      <c r="J172">
         <v>0</v>
       </c>
     </row>
@@ -4777,43 +6923,43 @@
   <sheetData>
     <row r="5" spans="1:4">
       <c r="B5" t="s">
-        <v>411</v>
+        <v>615</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>412</v>
+        <v>616</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" t="s">
-        <v>413</v>
+        <v>617</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" t="s">
-        <v>414</v>
+        <v>618</v>
       </c>
       <c r="C9">
-        <v>94</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -4828,7 +6974,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true" style="0"/>
@@ -4841,39 +6987,55 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>418</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>28</v>
+        <v>310</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4904,19 +7066,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>623</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>420</v>
+        <v>624</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>421</v>
+        <v>625</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>422</v>
+        <v>626</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>423</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4924,24 +7086,24 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>311000.0</v>
+        <v>626467.0</v>
       </c>
       <c r="F2">
-        <v>159911.0</v>
+        <v>373821.0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>628</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4953,10 +7115,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -4980,79 +7142,79 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>629</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>427</v>
+        <v>631</v>
       </c>
       <c r="B2">
-        <v>94</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>428</v>
+        <v>632</v>
       </c>
       <c r="B3">
-        <v>82</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>429</v>
+        <v>633</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>430</v>
+        <v>634</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>635</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>432</v>
+        <v>636</v>
       </c>
       <c r="B7">
-        <v>311000.0</v>
+        <v>626467.0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>433</v>
+        <v>637</v>
       </c>
       <c r="B8">
-        <v>11583</v>
+        <v>25668</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>434</v>
+        <v>638</v>
       </c>
       <c r="B9">
-        <v>11048</v>
+        <v>24001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>435</v>
+        <v>639</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5060,26 +7222,26 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>436</v>
+        <v>640</v>
       </c>
       <c r="B11">
-        <v>159911.0</v>
+        <v>373821.0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>437</v>
+        <v>641</v>
       </c>
       <c r="B12">
-        <v>36865.0</v>
+        <v>54333.0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>438</v>
+        <v>642</v>
       </c>
       <c r="B13">
-        <v>82</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
